--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEVADA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEVADA_2020.xlsx
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C78">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C92">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C140">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C163">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C203">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C224">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C232">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C239">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C362">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C639">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C657">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C697">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C778">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C838">
